--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:37</t>
+    <t xml:space="preserve">2026-09-09 22:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:23</t>
+    <t xml:space="preserve">2026-09-12 19:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_atacama.xlsx
@@ -39,30 +39,30 @@
     <t xml:space="preserve">Tierra Amarilla</t>
   </si>
   <si>
+    <t xml:space="preserve">Huasco</t>
+  </si>
+  <si>
     <t xml:space="preserve">Diego de Almagro</t>
   </si>
   <si>
+    <t xml:space="preserve">Caldera</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alto del Carmen</t>
   </si>
   <si>
-    <t xml:space="preserve">Huasco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caldera</t>
-  </si>
-  <si>
     <t xml:space="preserve">Freirina</t>
   </si>
   <si>
     <t xml:space="preserve">Chañaral</t>
   </si>
   <si>
+    <t xml:space="preserve">Vallenar</t>
+  </si>
+  <si>
     <t xml:space="preserve">Copiapó</t>
   </si>
   <si>
-    <t xml:space="preserve">Vallenar</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:40</t>
+    <t xml:space="preserve">2026-09-24 00:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -508,7 +508,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>54.98</v>
+        <v>22.04</v>
       </c>
     </row>
     <row r="3">
@@ -519,13 +519,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3202</v>
+        <v>3304</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>44.69</v>
+        <v>19.39</v>
       </c>
     </row>
     <row r="4">
@@ -536,13 +536,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3302</v>
+        <v>3202</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>42.58</v>
+        <v>19.02</v>
       </c>
     </row>
     <row r="5">
@@ -553,13 +553,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3304</v>
+        <v>3102</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>42.44</v>
+        <v>18.39</v>
       </c>
     </row>
     <row r="6">
@@ -570,13 +570,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>3102</v>
+        <v>3302</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>41.6</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="7">
@@ -593,7 +593,7 @@
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>38.2</v>
+        <v>17.15</v>
       </c>
     </row>
     <row r="8">
@@ -610,7 +610,7 @@
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>32.16</v>
+        <v>12.65</v>
       </c>
     </row>
     <row r="9">
@@ -621,13 +621,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3101</v>
+        <v>3301</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>23.91</v>
+        <v>10.02</v>
       </c>
     </row>
     <row r="10">
@@ -638,13 +638,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>3301</v>
+        <v>3101</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>23.5</v>
+        <v>9.9</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:17</t>
+    <t xml:space="preserve">2026-09-27 22:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:07</t>
+    <t xml:space="preserve">2026-09-29 11:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -508,7 +508,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>22.04</v>
+        <v>220.45</v>
       </c>
     </row>
     <row r="3">
@@ -525,7 +525,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>19.39</v>
+        <v>193.94</v>
       </c>
     </row>
     <row r="4">
@@ -542,7 +542,7 @@
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>19.02</v>
+        <v>190.18</v>
       </c>
     </row>
     <row r="5">
@@ -559,7 +559,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>18.39</v>
+        <v>183.89</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>18.18</v>
+        <v>181.8</v>
       </c>
     </row>
     <row r="7">
@@ -593,7 +593,7 @@
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>17.15</v>
+        <v>171.5</v>
       </c>
     </row>
     <row r="8">
@@ -610,7 +610,7 @@
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>12.65</v>
+        <v>126.49</v>
       </c>
     </row>
     <row r="9">
@@ -627,7 +627,7 @@
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>10.02</v>
+        <v>100.19</v>
       </c>
     </row>
     <row r="10">
@@ -644,7 +644,7 @@
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>9.9</v>
+        <v>98.96</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 11:01</t>
+    <t xml:space="preserve">2026-10-01 19:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -90,7 +90,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:26</t>
+    <t xml:space="preserve">2026-10-02 13:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:05</t>
+    <t xml:space="preserve">2026-10-05 07:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
